--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,29 +653,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1546</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F12" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F13" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F14" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F15" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F18" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>355671</v>
+        <v>0.631159</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>0.511964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,82 +864,82 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.561276</v>
+        <v>-0.413399</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.413399</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.413447</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="F24" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.972464</v>
+        <v>4.139781</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742264</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>2.311409</v>
+        <v>11.88673</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461065</v>
+        <v>4.724907</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>4.139781</v>
+        <v>10.700862</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="F28" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>10.700862</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>11.919595</v>
+        <v>0.003276</v>
       </c>
       <c r="F30" t="n">
-        <v>4.420848</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,35 +647,35 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1552</v>
+        <v>5.1329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>7299615</v>
+        <v>5.1323</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F12" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F13" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F14" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F16" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F17" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.631159</v>
+        <v>355671</v>
       </c>
       <c r="F19" t="n">
-        <v>0.511964</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,82 +864,82 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.641498</v>
+        <v>0.631159</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.561276</v>
+        <v>0.511964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>0.423696</v>
+        <v>-0.641498</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.413399</v>
+        <v>-3.561276</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>1.736829</v>
+        <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>0.565068</v>
+        <v>-0.844183</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>0.972464</v>
+        <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.742264</v>
+        <v>-0.8442809999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.311409</v>
+        <v>1.736829</v>
       </c>
       <c r="F24" t="n">
-        <v>0.461065</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>4.139781</v>
+        <v>0.972464</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.964334</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>11.88673</v>
+        <v>2.311409</v>
       </c>
       <c r="F26" t="n">
-        <v>4.724907</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>10.700862</v>
+        <v>4.139781</v>
       </c>
       <c r="F27" t="n">
-        <v>3.177699</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>11.919595</v>
+        <v>11.88673</v>
       </c>
       <c r="F28" t="n">
-        <v>4.420848</v>
+        <v>4.724907</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>10.700862</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.003276</v>
+        <v>11.919595</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000497</v>
+        <v>4.420848</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F32" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.66</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -528,16 +528,16 @@
         <v>44408</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
         <v>0.96</v>
       </c>
       <c r="F5" t="n">
-        <v>0.58</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
@@ -572,16 +572,16 @@
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>1.02</v>
       </c>
       <c r="F7" t="n">
-        <v>0.65</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1329</v>
+        <v>5.1088</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1323</v>
+        <v>5.1082</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.844183</v>
+        <v>-1.30974</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8442809999999999</v>
+        <v>-1.309892</v>
       </c>
     </row>
     <row r="24">
@@ -1034,16 +1034,16 @@
         <v>44742</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
         <v>11.88673</v>
       </c>
       <c r="F28" t="n">
-        <v>4.724907</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
@@ -1078,16 +1078,16 @@
         <v>44742</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
         <v>11.919595</v>
       </c>
       <c r="F30" t="n">
-        <v>4.420848</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>1.02</v>
+        <v>96.42256999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14</v>
+        <v>111.15205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>96.42256999999999</v>
+        <v>99.83515</v>
       </c>
       <c r="F8" t="n">
-        <v>111.15205</v>
+        <v>113.72712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.83515</v>
+        <v>5.1216</v>
       </c>
       <c r="F9" t="n">
-        <v>113.72712</v>
+        <v>5.1088</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1088</v>
+        <v>5.1082</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1082</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F12" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F13" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F14" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F15" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F18" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>355671</v>
+        <v>0.631159</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>0.511964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.561276</v>
+        <v>-1.30974</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.30974</v>
+        <v>-1.309892</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.309892</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="F24" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.311409</v>
+        <v>4.139781</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461065</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>4.139781</v>
+        <v>11.88673</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>10.700862</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>11.919595</v>
+        <v>0.003276</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>96.42256999999999</v>
+        <v>1.02</v>
       </c>
       <c r="F7" t="n">
-        <v>111.15205</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>99.83515</v>
+        <v>96.42256999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>113.72712</v>
+        <v>111.15205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1216</v>
+        <v>99.83515</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1088</v>
+        <v>113.72712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.121</v>
+        <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1082</v>
+        <v>5.1183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>7299615</v>
+        <v>5.1177</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F12" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F13" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F14" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F16" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F17" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.631159</v>
+        <v>355671</v>
       </c>
       <c r="F19" t="n">
-        <v>0.511964</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.641498</v>
+        <v>0.631159</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.561276</v>
+        <v>0.511964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>0.423696</v>
+        <v>-0.641498</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.30974</v>
+        <v>-3.561276</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423745</v>
+        <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.309892</v>
+        <v>-1.126222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.736829</v>
+        <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.565068</v>
+        <v>-1.126352</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.972464</v>
+        <v>1.736829</v>
       </c>
       <c r="F24" t="n">
-        <v>0.742264</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.311409</v>
+        <v>0.972464</v>
       </c>
       <c r="F25" t="n">
-        <v>0.461065</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>4.139781</v>
+        <v>2.311409</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.964334</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>11.88673</v>
+        <v>4.139781</v>
       </c>
       <c r="F27" t="n">
-        <v>4.641328</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>11.919595</v>
+        <v>11.88673</v>
       </c>
       <c r="F28" t="n">
-        <v>4.327084</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>10.700862</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.003276</v>
+        <v>11.919595</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000497</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F32" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.66</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1183</v>
+        <v>5.0742</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1177</v>
+        <v>5.0736</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.126222</v>
+        <v>-1.978132</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.126352</v>
+        <v>-1.978362</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0742</v>
+        <v>5.0727</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0736</v>
+        <v>5.0721</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +785,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F18" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>355671</v>
+        <v>0.631159</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>0.511964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.561276</v>
+        <v>-2.007109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.978132</v>
+        <v>-2.007342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.978362</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="F24" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.311409</v>
+        <v>4.139781</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461065</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>4.139781</v>
+        <v>11.88673</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>11.919595</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F17" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.631159</v>
+        <v>355671</v>
       </c>
       <c r="F19" t="n">
-        <v>0.511964</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.641498</v>
+        <v>0.631159</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.561276</v>
+        <v>0.511964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>0.423696</v>
+        <v>-0.641498</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.007109</v>
+        <v>-3.561276</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423745</v>
+        <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.007342</v>
+        <v>-2.007109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.736829</v>
+        <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.565068</v>
+        <v>-2.007342</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.972464</v>
+        <v>1.736829</v>
       </c>
       <c r="F24" t="n">
-        <v>0.742264</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.311409</v>
+        <v>0.972464</v>
       </c>
       <c r="F25" t="n">
-        <v>0.461065</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>4.139781</v>
+        <v>2.311409</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.964334</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>11.88673</v>
+        <v>4.139781</v>
       </c>
       <c r="F27" t="n">
-        <v>4.641328</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>10.700862</v>
+        <v>11.88673</v>
       </c>
       <c r="F28" t="n">
-        <v>3.177699</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>11.919595</v>
+        <v>10.700862</v>
       </c>
       <c r="F29" t="n">
-        <v>4.327084</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>11.919595</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F33" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.66</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0727</v>
+        <v>5.0975</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0721</v>
+        <v>5.0969</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.007109</v>
+        <v>-1.52803</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.007342</v>
+        <v>-1.528207</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -594,16 +594,16 @@
         <v>44408</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.42256999999999</v>
+        <v>96.31464</v>
       </c>
       <c r="F8" t="n">
-        <v>111.15205</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
@@ -616,16 +616,16 @@
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>99.83515</v>
+        <v>99.83978</v>
       </c>
       <c r="F9" t="n">
-        <v>113.72712</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0975</v>
+        <v>5.1176</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0969</v>
+        <v>5.117</v>
       </c>
     </row>
     <row r="12">
@@ -858,16 +858,16 @@
         <v>44439</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.631159</v>
+        <v>0.79016</v>
       </c>
       <c r="F20" t="n">
-        <v>0.511964</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="21">
@@ -880,16 +880,16 @@
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.641498</v>
+        <v>-0.512311</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.561276</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.52803</v>
+        <v>-1.139744</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.528207</v>
+        <v>-1.139876</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1176</v>
+        <v>5.0894</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.117</v>
+        <v>5.0888</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.139744</v>
+        <v>-1.684503</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.139876</v>
+        <v>-1.684699</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0894</v>
+        <v>5.078</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0888</v>
+        <v>5.0774</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.684503</v>
+        <v>-1.904725</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.684699</v>
+        <v>-1.904946</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.078</v>
+        <v>5.0638</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0774</v>
+        <v>5.0632</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.904725</v>
+        <v>-2.179036</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.904946</v>
+        <v>-2.179289</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0638</v>
+        <v>5.0807</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0632</v>
+        <v>5.0801</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.179036</v>
+        <v>-1.852567</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.179289</v>
+        <v>-1.852782</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052531</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="F5" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.02</v>
+        <v>96.31464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.0666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0807</v>
+        <v>5.066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0801</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F12" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F13" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F14" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F15" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F18" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>355671</v>
+        <v>0.79016</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.79016</v>
+        <v>-0.512311</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.512311</v>
+        <v>0.423696</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.915762</v>
+        <v>-2.124947</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.852567</v>
+        <v>-2.125193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.852782</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="F24" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.311409</v>
+        <v>4.139781</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461065</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>4.139781</v>
+        <v>11.88673</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>11.919595</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.96</v>
+        <v>0.016137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.16</v>
+        <v>0.052531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>96.31464</v>
+        <v>1.02</v>
       </c>
       <c r="F7" t="n">
-        <v>111.03587</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>99.83978</v>
+        <v>96.31464</v>
       </c>
       <c r="F8" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1216</v>
+        <v>99.83978</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0666</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.121</v>
+        <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.066</v>
+        <v>5.0666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>7299615</v>
+        <v>5.066</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F12" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F13" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F14" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F16" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F17" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.79016</v>
+        <v>355671</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07079299999999999</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.512311</v>
+        <v>0.79016</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.915762</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>0.423696</v>
+        <v>-0.512311</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.124947</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423745</v>
+        <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.125193</v>
+        <v>-2.124947</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.736829</v>
+        <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.565068</v>
+        <v>-2.125193</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.972464</v>
+        <v>1.736829</v>
       </c>
       <c r="F24" t="n">
-        <v>0.742264</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.311409</v>
+        <v>0.972464</v>
       </c>
       <c r="F25" t="n">
-        <v>0.461065</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>4.139781</v>
+        <v>2.311409</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.964334</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>11.88673</v>
+        <v>4.139781</v>
       </c>
       <c r="F27" t="n">
-        <v>4.641328</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>10.700862</v>
+        <v>11.88673</v>
       </c>
       <c r="F28" t="n">
-        <v>3.177699</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>11.919595</v>
+        <v>10.700862</v>
       </c>
       <c r="F29" t="n">
-        <v>4.327084</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>11.919595</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F32" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.66</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.0666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0666</v>
+        <v>5.066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F11" t="n">
-        <v>5.066</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F12" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F13" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F14" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F15" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,148 +798,148 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F18" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>355671</v>
+        <v>-0.512311</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>0.79016</v>
+        <v>0.423696</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07079299999999999</v>
+        <v>-2.124947</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.512311</v>
+        <v>0.423745</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.915762</v>
+        <v>-2.125193</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.124947</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.125193</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="F24" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.972464</v>
+        <v>4.139781</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742264</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>2.311409</v>
+        <v>11.88673</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461065</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>4.139781</v>
+        <v>10.700862</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>10.700862</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>11.919595</v>
+        <v>0.003276</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>99.83978</v>
+        <v>96.31464</v>
       </c>
       <c r="F8" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1216</v>
+        <v>99.83978</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0666</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.121</v>
+        <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>5.066</v>
+        <v>5.1005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>7299615</v>
+        <v>5.0998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F12" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F13" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F14" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F16" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,148 +798,148 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F17" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.512311</v>
+        <v>355671</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.915762</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.423696</v>
+        <v>0.79016</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.124947</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>0.423745</v>
+        <v>-0.512311</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.125193</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>1.736829</v>
+        <v>0.423696</v>
       </c>
       <c r="F22" t="n">
-        <v>0.565068</v>
+        <v>-1.470077</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>0.972464</v>
+        <v>0.423745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.742264</v>
+        <v>-1.472179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,82 +952,82 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.311409</v>
+        <v>1.736829</v>
       </c>
       <c r="F24" t="n">
-        <v>0.461065</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>4.139781</v>
+        <v>0.972464</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.964334</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>11.88673</v>
+        <v>2.311409</v>
       </c>
       <c r="F26" t="n">
-        <v>4.641328</v>
+        <v>0.461065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>10.700862</v>
+        <v>4.139781</v>
       </c>
       <c r="F27" t="n">
-        <v>3.177699</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,60 +1040,60 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>11.919595</v>
+        <v>11.88673</v>
       </c>
       <c r="F28" t="n">
-        <v>4.327084</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>10.700862</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>0.003276</v>
+        <v>11.919595</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000497</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F32" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,7 +1172,7 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
         <v>0.11</v>
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.66</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052531</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="F5" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,126 +556,126 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.02</v>
+        <v>99.83978</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>96.31464</v>
+        <v>5.1216</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>5.1177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.83978</v>
+        <v>5.121</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.1171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1005</v>
+        <v>7299615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0998</v>
+        <v>2704550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4271865</v>
+        <v>2.36</v>
       </c>
       <c r="F12" t="n">
-        <v>7299615</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1833179</v>
+        <v>1.58</v>
       </c>
       <c r="F13" t="n">
-        <v>2704550</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2438686</v>
+        <v>2.94</v>
       </c>
       <c r="F14" t="n">
-        <v>4595065</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,104 +754,104 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>20.26</v>
       </c>
       <c r="F15" t="n">
-        <v>4.74</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.58</v>
+        <v>355671</v>
       </c>
       <c r="F16" t="n">
-        <v>3.24</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>2.94</v>
+        <v>-0.512311</v>
       </c>
       <c r="F17" t="n">
-        <v>5.62</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26</v>
+        <v>0.423696</v>
       </c>
       <c r="F18" t="n">
-        <v>33.42</v>
+        <v>-1.137812</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>355671</v>
+        <v>0.423745</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>-1.137944</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,16 +864,16 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.79016</v>
+        <v>1.736829</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.565068</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -886,361 +886,229 @@
         <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.512311</v>
+        <v>0.972464</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.915762</v>
+        <v>0.742264</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423696</v>
+        <v>4.139781</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.470077</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>0.423745</v>
+        <v>11.88673</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.472179</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>1.736829</v>
+        <v>10.700862</v>
       </c>
       <c r="F24" t="n">
-        <v>0.565068</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>0.972464</v>
+        <v>11.919595</v>
       </c>
       <c r="F25" t="n">
-        <v>0.742264</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>2.311409</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>4.139781</v>
+        <v>0.003276</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>11.88673</v>
+        <v>0.01</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>10.700862</v>
+        <v>-0.02</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177699</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>11.919595</v>
+        <v>0.02</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D32" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-0.000497</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dif_cdi</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D33" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.000497</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F37" t="n">
         <v>-0.09</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.96</v>
+        <v>0.016137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.16</v>
+        <v>0.052531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,214 +556,214 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>99.83978</v>
+        <v>1.02</v>
       </c>
       <c r="F7" t="n">
-        <v>109.52993</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1216</v>
+        <v>96.31464</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1177</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.121</v>
+        <v>99.83978</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1171</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>4271865</v>
+        <v>5.1216</v>
       </c>
       <c r="F10" t="n">
-        <v>7299615</v>
+        <v>5.1217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1833179</v>
+        <v>5.121</v>
       </c>
       <c r="F11" t="n">
-        <v>2704550</v>
+        <v>5.1211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>2.36</v>
+        <v>4271865</v>
       </c>
       <c r="F12" t="n">
-        <v>4.74</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>1.58</v>
+        <v>1833179</v>
       </c>
       <c r="F13" t="n">
-        <v>3.24</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2.94</v>
+        <v>2438686</v>
       </c>
       <c r="F14" t="n">
-        <v>5.62</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>20.26</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>33.42</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,82 +776,82 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>355671</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>367558</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.512311</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.915762</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>0.423696</v>
+        <v>355671</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.137812</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>0.423745</v>
+        <v>0.79016</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.137944</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,252 +864,340 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>1.736829</v>
+        <v>-0.512311</v>
       </c>
       <c r="F20" t="n">
-        <v>0.565068</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>0.972464</v>
+        <v>0.423696</v>
       </c>
       <c r="F21" t="n">
-        <v>0.742264</v>
+        <v>-1.060542</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>4.139781</v>
+        <v>0.423745</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.964334</v>
+        <v>-1.060665</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>11.88673</v>
+        <v>1.736829</v>
       </c>
       <c r="F23" t="n">
-        <v>4.641328</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>10.700862</v>
+        <v>0.972464</v>
       </c>
       <c r="F24" t="n">
-        <v>3.177699</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>11.919595</v>
+        <v>2.311409</v>
       </c>
       <c r="F25" t="n">
-        <v>4.327084</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4.139781</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>0.003276</v>
+        <v>11.88673</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.000497</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01</v>
+        <v>10.700862</v>
       </c>
       <c r="F28" t="n">
-        <v>0.11</v>
+        <v>3.177699</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.02</v>
+        <v>11.919595</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.000497</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.000497</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D33" t="n">
+        <v>59</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>59</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D31" t="n">
-        <v>58</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="B35" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D35" t="n">
+        <v>59</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.66</v>
       </c>
-      <c r="F31" t="n">
-        <v>-0.09</v>
+      <c r="F35" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>0.016137</v>
+        <v>0.019413</v>
       </c>
       <c r="F3" t="n">
         <v>0.052531</v>
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016137</v>
+        <v>0.019413</v>
       </c>
       <c r="F4" t="n">
         <v>0.052531</v>
@@ -550,16 +550,16 @@
         <v>44408</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>0.78</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="7">
@@ -587,95 +587,95 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>96.31464</v>
+        <v>5.1433</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>5.0739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>99.83978</v>
+        <v>5.1427</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.0733</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1217</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1211</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>4271865</v>
+        <v>2438686</v>
       </c>
       <c r="F12" t="n">
-        <v>7355800</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>1833179</v>
+        <v>2.36</v>
       </c>
       <c r="F13" t="n">
-        <v>2749001</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>2438686</v>
+        <v>1.58</v>
       </c>
       <c r="F14" t="n">
-        <v>4606799</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="F15" t="n">
-        <v>4.68</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F16" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,126 +798,126 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F17" t="n">
-        <v>33.44</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>355671</v>
+        <v>5.757004</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>-1.983928</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>0.79016</v>
+        <v>5.757676</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07079299999999999</v>
+        <v>-1.984158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.512311</v>
+        <v>1.736829</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.915762</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>0.423696</v>
+        <v>0.972464</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.060542</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>0.423745</v>
+        <v>2.311409</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.060665</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -930,214 +930,214 @@
         <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>1.736829</v>
+        <v>4.139781</v>
       </c>
       <c r="F23" t="n">
-        <v>0.714468</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>0.972464</v>
+        <v>11.88673</v>
       </c>
       <c r="F24" t="n">
-        <v>1.515494</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E25" t="n">
-        <v>2.311409</v>
+        <v>10.700862</v>
       </c>
       <c r="F25" t="n">
-        <v>0.242446</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>4.139781</v>
+        <v>11.919595</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.964334</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>11.88673</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4.641328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E28" t="n">
-        <v>10.700862</v>
+        <v>0.001591</v>
       </c>
       <c r="F28" t="n">
-        <v>3.177699</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>11.919595</v>
+        <v>0.001591</v>
       </c>
       <c r="F29" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003276</v>
+        <v>0.02</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000497</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1150,53 +1150,9 @@
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01</v>
+        <v>0.66</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D34" t="n">
-        <v>59</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D35" t="n">
-        <v>59</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F35" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,16 +459,16 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="F2" t="n">
         <v>14.25</v>
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="F5" t="n">
         <v>0.16</v>
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="n">
         <v>-1.16</v>
@@ -569,16 +569,16 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
         <v>0.14</v>
@@ -587,572 +587,660 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1433</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>5.0739</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1427</v>
+        <v>99.32829</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0733</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D10" t="n">
         <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>4271865</v>
+        <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>7355800</v>
+        <v>5.0773</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>1833179</v>
+        <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>2749001</v>
+        <v>5.0767</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>2438686</v>
+        <v>4346060</v>
       </c>
       <c r="F12" t="n">
-        <v>4606799</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2.36</v>
+        <v>1851006</v>
       </c>
       <c r="F13" t="n">
-        <v>4.68</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>1.58</v>
+        <v>2495054</v>
       </c>
       <c r="F14" t="n">
-        <v>3.19</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="F15" t="n">
-        <v>5.57</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>20.26</v>
+        <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>33.44</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>355671</v>
+        <v>2.96</v>
       </c>
       <c r="F17" t="n">
-        <v>367558</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>5.757004</v>
+        <v>20.92</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.983928</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
         <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>5.757676</v>
+        <v>370395</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.984158</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1.736829</v>
+        <v>-0.119484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.714468</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>0.972464</v>
+        <v>-2.094902</v>
       </c>
       <c r="F21" t="n">
-        <v>1.515494</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D22" t="n">
         <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>2.311409</v>
+        <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>0.242446</v>
+        <v>-1.918247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
         <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>4.139781</v>
+        <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.964334</v>
+        <v>-1.91847</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>11.88673</v>
+        <v>2.185796</v>
       </c>
       <c r="F24" t="n">
-        <v>4.641328</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>10.700862</v>
+        <v>2.329166</v>
       </c>
       <c r="F25" t="n">
-        <v>2.772183</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>11.919595</v>
+        <v>2.079394</v>
       </c>
       <c r="F26" t="n">
-        <v>4.327084</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>-0.407403</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001591</v>
+        <v>10.069235</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.000497</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001591</v>
+        <v>10.074751</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000497</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01</v>
+        <v>10.124804</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.06</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.02</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
         <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02</v>
+        <v>0.001591</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.05</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D33" t="n">
+        <v>59</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.000497</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D33" t="n">
-        <v>59</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F33" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>0.019413</v>
+        <v>0.019569</v>
       </c>
       <c r="F3" t="n">
         <v>0.052531</v>
@@ -512,7 +512,7 @@
         <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.019413</v>
+        <v>0.019569</v>
       </c>
       <c r="F4" t="n">
         <v>0.052531</v>
@@ -697,7 +697,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="F13" t="n">
-        <v>2749001</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F16" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F17" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F18" t="n">
-        <v>33.44</v>
+        <v>367558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>370395</v>
+        <v>-0.119484</v>
       </c>
       <c r="F19" t="n">
-        <v>367558</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.119484</v>
+        <v>-2.094902</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.094902</v>
+        <v>5.757004</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.915762</v>
+        <v>-1.918247</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.918247</v>
+        <v>-1.91847</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.91847</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="F24" t="n">
-        <v>0.714468</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.329166</v>
+        <v>-0.407403</v>
       </c>
       <c r="F25" t="n">
-        <v>1.515494</v>
+        <v>-0.964334</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>2.079394</v>
+        <v>10.069235</v>
       </c>
       <c r="F26" t="n">
-        <v>0.242446</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.407403</v>
+        <v>10.074751</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.964334</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,126 +1040,126 @@
         <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>10.074751</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
-        <v>10.124804</v>
+        <v>0.001435</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.001435</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,13 +484,13 @@
         <v>44439</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.019569</v>
+        <v>0.01974</v>
       </c>
       <c r="F3" t="n">
         <v>0.052531</v>
@@ -506,13 +506,13 @@
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.019569</v>
+        <v>0.01974</v>
       </c>
       <c r="F4" t="n">
         <v>0.052531</v>
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,82 +600,82 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.0723</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0773</v>
+        <v>5.0717</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0767</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4346060</v>
+        <v>2495054</v>
       </c>
       <c r="F12" t="n">
-        <v>7355800</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F13" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F14" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F15" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,214 +776,214 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F16" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F17" t="n">
-        <v>33.44</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>370395</v>
+        <v>-2.094902</v>
       </c>
       <c r="F18" t="n">
-        <v>367558</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.119484</v>
+        <v>5.757004</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07079299999999999</v>
+        <v>-0.098478</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.094902</v>
+        <v>5.757676</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.915762</v>
+        <v>-0.09848899999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.918247</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757676</v>
+        <v>2.079394</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.91847</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>2.185796</v>
+        <v>-0.407403</v>
       </c>
       <c r="F23" t="n">
-        <v>0.714468</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>2.079394</v>
+        <v>10.069235</v>
       </c>
       <c r="F24" t="n">
-        <v>0.242446</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.407403</v>
+        <v>10.074751</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.964334</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,60 +996,60 @@
         <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="F26" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>10.074751</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>10.124804</v>
+        <v>0.001263</v>
       </c>
       <c r="F28" t="n">
-        <v>4.327084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,7 +1062,7 @@
         <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.001263</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1071,51 +1071,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001435</v>
+        <v>-0.03</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001435</v>
+        <v>-0.13</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1128,16 +1128,16 @@
         <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1150,53 +1150,9 @@
         <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F35" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01974</v>
+        <v>0.01993</v>
       </c>
       <c r="F3" t="n">
         <v>0.052531</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01974</v>
+        <v>0.01993</v>
       </c>
       <c r="F4" t="n">
         <v>0.052531</v>
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>99.32829</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1433</v>
+        <v>99.32829</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0723</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,10 +644,10 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1427</v>
+        <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0717</v>
+        <v>5.1053</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>2495054</v>
+        <v>1851006</v>
       </c>
       <c r="F12" t="n">
-        <v>4606799</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2.37</v>
+        <v>2495054</v>
       </c>
       <c r="F13" t="n">
-        <v>4.68</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>3.19</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>5.57</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,126 +776,126 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>20.92</v>
+        <v>2.96</v>
       </c>
       <c r="F16" t="n">
-        <v>33.44</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>370395</v>
+        <v>20.92</v>
       </c>
       <c r="F17" t="n">
-        <v>369742</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.094902</v>
+        <v>370395</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.915762</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>5.757004</v>
+        <v>-0.119484</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.098478</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>5.757676</v>
+        <v>-2.094902</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.09848899999999999</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>2.185796</v>
+        <v>5.757004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.714468</v>
+        <v>0.551474</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,82 +908,82 @@
         <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>2.079394</v>
+        <v>2.185796</v>
       </c>
       <c r="F22" t="n">
-        <v>0.242446</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.407403</v>
+        <v>2.329166</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5941920000000001</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>10.069235</v>
+        <v>2.079394</v>
       </c>
       <c r="F24" t="n">
-        <v>4.641328</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>10.074751</v>
+        <v>-0.407403</v>
       </c>
       <c r="F25" t="n">
-        <v>2.772183</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,60 +996,60 @@
         <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>10.124804</v>
+        <v>10.069235</v>
       </c>
       <c r="F26" t="n">
-        <v>4.327084</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>10.074751</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001263</v>
+        <v>10.124804</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,7 +1062,7 @@
         <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001263</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1071,51 +1071,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.03</v>
+        <v>0.001073</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.13</v>
+        <v>0.001073</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1128,16 +1128,16 @@
         <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1150,9 +1150,53 @@
         <v>58</v>
       </c>
       <c r="E33" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.5</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F35" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>5.25</v>
+        <v>0.01993</v>
       </c>
       <c r="F2" t="n">
-        <v>14.25</v>
+        <v>0.052531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,161 +499,161 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01993</v>
+        <v>0.87</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052531</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F5" t="n">
-        <v>0.16</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>0.66</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.16</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>0.88</v>
+        <v>99.32829</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>97.07568000000001</v>
+        <v>5.1433</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>5.1154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.32829</v>
+        <v>5.1427</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.1148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1433</v>
+        <v>4346060</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1053</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -666,16 +666,16 @@
         <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>4346060</v>
+        <v>2495054</v>
       </c>
       <c r="F11" t="n">
-        <v>7355800</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1851006</v>
+        <v>2.37</v>
       </c>
       <c r="F12" t="n">
-        <v>2749001</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2495054</v>
+        <v>1.56</v>
       </c>
       <c r="F13" t="n">
-        <v>4606799</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.37</v>
+        <v>2.96</v>
       </c>
       <c r="F14" t="n">
-        <v>4.68</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,148 +754,148 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>20.92</v>
       </c>
       <c r="F15" t="n">
-        <v>3.19</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>2.96</v>
+        <v>370395</v>
       </c>
       <c r="F16" t="n">
-        <v>5.57</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
-        <v>20.92</v>
+        <v>-0.119484</v>
       </c>
       <c r="F17" t="n">
-        <v>33.44</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>370395</v>
+        <v>-2.094902</v>
       </c>
       <c r="F18" t="n">
-        <v>369742</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.119484</v>
+        <v>5.757004</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.750399</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.094902</v>
+        <v>5.757676</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.915762</v>
+        <v>0.750488</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="F21" t="n">
-        <v>0.551474</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,295 +908,207 @@
         <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="F22" t="n">
-        <v>0.714468</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>2.329166</v>
+        <v>-0.407403</v>
       </c>
       <c r="F23" t="n">
-        <v>1.515494</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>2.079394</v>
+        <v>10.069235</v>
       </c>
       <c r="F24" t="n">
-        <v>0.242446</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.407403</v>
+        <v>10.074751</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>10.069235</v>
+        <v>0.001073</v>
       </c>
       <c r="F26" t="n">
-        <v>4.641328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>10.074751</v>
+        <v>0.001073</v>
       </c>
       <c r="F27" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>10.124804</v>
+        <v>-0.03</v>
       </c>
       <c r="F28" t="n">
-        <v>4.327084</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>-0.13</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001073</v>
+        <v>0.05</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001073</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D32" t="n">
-        <v>58</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D33" t="n">
-        <v>58</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F35" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01993</v>
+        <v>5.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.052531</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -493,189 +493,189 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.052531</v>
+        <v>0.052313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.87</v>
+        <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.16</v>
+        <v>0.052531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.16</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>97.07568000000001</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="n">
-        <v>111.03587</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>99.32829</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>109.52993</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1433</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1154</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1427</v>
+        <v>99.32829</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1148</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>4346060</v>
+        <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>7355800</v>
+        <v>5.1017</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>2495054</v>
+        <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>4606799</v>
+        <v>5.1011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>2.37</v>
+        <v>4346060</v>
       </c>
       <c r="F12" t="n">
-        <v>4.68</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1.56</v>
+        <v>1851006</v>
       </c>
       <c r="F13" t="n">
-        <v>3.19</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.96</v>
+        <v>2495054</v>
       </c>
       <c r="F14" t="n">
-        <v>5.57</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,361 +754,493 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>20.92</v>
+        <v>2.37</v>
       </c>
       <c r="F15" t="n">
-        <v>33.44</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>370395</v>
+        <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>369742</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.119484</v>
+        <v>2.96</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07079299999999999</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.094902</v>
+        <v>20.92</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.915762</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>5.757004</v>
+        <v>370395</v>
       </c>
       <c r="F19" t="n">
-        <v>0.750399</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>5.757676</v>
+        <v>-0.119484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.750488</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>2.185796</v>
+        <v>-2.094902</v>
       </c>
       <c r="F21" t="n">
-        <v>0.714468</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>2.079394</v>
+        <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>0.242446</v>
+        <v>0.48057</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.407403</v>
+        <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.480627</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>10.069235</v>
+        <v>2.185796</v>
       </c>
       <c r="F24" t="n">
-        <v>4.641328</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>10.074751</v>
+        <v>2.329166</v>
       </c>
       <c r="F25" t="n">
-        <v>2.772183</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001073</v>
+        <v>2.079394</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001073</v>
+        <v>-0.407403</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.03</v>
+        <v>10.069235</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.06</v>
+        <v>4.641328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.13</v>
+        <v>10.074751</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.06</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05</v>
+        <v>10.124804</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.05</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.000218</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>58</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D37" t="n">
         <v>58</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E37" t="n">
         <v>0.5</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F37" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.052313</v>
+        <v>0.052183</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052531</v>
+        <v>0.052313</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1017</v>
+        <v>5.0908</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1011</v>
+        <v>5.0902</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>0.48057</v>
+        <v>0.265889</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.480627</v>
+        <v>0.265921</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000218</v>
+        <v>-0.000348</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-0.000218</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.052183</v>
+        <v>0.052095</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052313</v>
+        <v>0.052183</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0908</v>
+        <v>5.0963</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0902</v>
+        <v>5.0957</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>0.265889</v>
+        <v>0.374215</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.265921</v>
+        <v>0.374259</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000348</v>
+        <v>-0.000436</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000218</v>
+        <v>-0.000348</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>5.25</v>
+        <v>0.01993</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>0.052033</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,51 +499,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01993</v>
+        <v>0.87</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052183</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F5" t="n">
-        <v>0.16</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>0.88</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>5.1285</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0963</v>
+        <v>5.1279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0957</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="F12" t="n">
-        <v>7355800</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="F13" t="n">
-        <v>2749001</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F16" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F17" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F18" t="n">
-        <v>33.44</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>370395</v>
+        <v>-0.119484</v>
       </c>
       <c r="F19" t="n">
-        <v>369742</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.119484</v>
+        <v>-2.094902</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.094902</v>
+        <v>5.757004</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.915762</v>
+        <v>1.00841</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F22" t="n">
-        <v>0.374215</v>
+        <v>1.008529</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F23" t="n">
-        <v>0.374259</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F24" t="n">
-        <v>0.714468</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,82 +974,82 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F25" t="n">
-        <v>1.515494</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F26" t="n">
-        <v>0.242446</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.641328</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F29" t="n">
-        <v>2.772183</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>10.124804</v>
+        <v>0.001073</v>
       </c>
       <c r="F30" t="n">
-        <v>4.327084</v>
+        <v>-0.000498</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001073</v>
+        <v>-0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000436</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001073</v>
+        <v>-0.13</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000348</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01993</v>
+        <v>5.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.052033</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.052095</v>
+        <v>0.051987</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +625,7 @@
         <v>5.1433</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1285</v>
+        <v>5.1639</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>5.1427</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1279</v>
+        <v>5.1632</v>
       </c>
     </row>
     <row r="11">
@@ -741,463 +741,331 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>370395</v>
       </c>
       <c r="F15" t="n">
-        <v>3.19</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" t="n">
-        <v>2.96</v>
+        <v>-0.119484</v>
       </c>
       <c r="F16" t="n">
-        <v>5.57</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
-        <v>20.92</v>
+        <v>-2.094902</v>
       </c>
       <c r="F17" t="n">
-        <v>33.44</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>370395</v>
+        <v>5.757004</v>
       </c>
       <c r="F18" t="n">
-        <v>369742</v>
+        <v>1.705631</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.119484</v>
+        <v>5.757676</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07079299999999999</v>
+        <v>1.703863</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.094902</v>
+        <v>2.185796</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.915762</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>5.757004</v>
+        <v>2.329166</v>
       </c>
       <c r="F21" t="n">
-        <v>1.00841</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757676</v>
+        <v>2.079394</v>
       </c>
       <c r="F22" t="n">
-        <v>1.008529</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>2.185796</v>
+        <v>-0.407403</v>
       </c>
       <c r="F23" t="n">
-        <v>0.714468</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>2.329166</v>
+        <v>10.069235</v>
       </c>
       <c r="F24" t="n">
-        <v>1.515494</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>2.079394</v>
+        <v>10.074751</v>
       </c>
       <c r="F25" t="n">
-        <v>0.242446</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.407403</v>
+        <v>10.124804</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>10.069235</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4.443025</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>10.074751</v>
+        <v>0.001073</v>
       </c>
       <c r="F28" t="n">
-        <v>2.772183</v>
+        <v>-0.000544</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>10.124804</v>
+        <v>-0.03</v>
       </c>
       <c r="F29" t="n">
-        <v>4.098046</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D30" t="n">
-        <v>60</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.001073</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-0.000498</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>dif_cdi</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.001073</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-0.000436</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D32" t="n">
-        <v>58</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F32" t="n">
         <v>-0.06</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D33" t="n">
-        <v>58</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,35 +493,35 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051987</v>
+        <v>0.05195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.87</v>
+        <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051987</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.16</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.07568000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>111.03587</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>99.32829</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1433</v>
+        <v>99.32829</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1639</v>
+        <v>109.52993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1427</v>
+        <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1632</v>
+        <v>5.1859</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4346060</v>
+        <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>7355800</v>
+        <v>5.1853</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1851006</v>
+        <v>4346060</v>
       </c>
       <c r="F12" t="n">
-        <v>2749001</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2495054</v>
+        <v>1851006</v>
       </c>
       <c r="F13" t="n">
-        <v>4606799</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,340 +732,516 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.37</v>
+        <v>2495054</v>
       </c>
       <c r="F14" t="n">
-        <v>4.68</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>370395</v>
+        <v>2.37</v>
       </c>
       <c r="F15" t="n">
-        <v>369742</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.119484</v>
+        <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07079299999999999</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.094902</v>
+        <v>2.96</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.915762</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>5.757004</v>
+        <v>20.92</v>
       </c>
       <c r="F18" t="n">
-        <v>1.705631</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>5.757676</v>
+        <v>370395</v>
       </c>
       <c r="F19" t="n">
-        <v>1.703863</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>2.185796</v>
+        <v>-0.119484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.714468</v>
+        <v>0.07079299999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>2.329166</v>
+        <v>-2.094902</v>
       </c>
       <c r="F21" t="n">
-        <v>1.515494</v>
+        <v>-3.915762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>2.079394</v>
+        <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>0.242446</v>
+        <v>2.138932</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.407403</v>
+        <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.139185</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>10.069235</v>
+        <v>2.185796</v>
       </c>
       <c r="F24" t="n">
-        <v>4.443025</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>10.074751</v>
+        <v>2.329166</v>
       </c>
       <c r="F25" t="n">
-        <v>2.772183</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>10.124804</v>
+        <v>2.079394</v>
       </c>
       <c r="F26" t="n">
-        <v>4.098046</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>-0.407403</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.25</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001073</v>
+        <v>10.069235</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.000544</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>igp_m_acum_12m</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D29" t="n">
+        <v>49</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10.074751</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.772183</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>inpc_acum_12m</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D30" t="n">
+        <v>49</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10.124804</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.098046</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.000581</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.000544</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="B34" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D34" t="n">
         <v>58</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E34" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F34" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05195</v>
+        <v>0.051921</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051987</v>
+        <v>0.05195</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1859</v>
+        <v>5.2236</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1853</v>
+        <v>5.223</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>2.138932</v>
+        <v>2.881453</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>2.139185</v>
+        <v>2.881793</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000581</v>
+        <v>-0.00061</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000544</v>
+        <v>-0.000581</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051921</v>
+        <v>0.051898</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05195</v>
+        <v>0.051921</v>
       </c>
     </row>
     <row r="5">
@@ -594,16 +594,16 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.07568000000001</v>
+        <v>97.01608</v>
       </c>
       <c r="F8" t="n">
-        <v>111.03587</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="9">
@@ -616,16 +616,16 @@
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>99.32829</v>
+        <v>99.19190999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>109.52993</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2236</v>
+        <v>5.2014</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.223</v>
+        <v>5.2008</v>
       </c>
     </row>
     <row r="12">
@@ -858,16 +858,16 @@
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.119484</v>
+        <v>-0.064886</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07079299999999999</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
@@ -880,16 +880,16 @@
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.094902</v>
+        <v>-2.103216</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.915762</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>2.881453</v>
+        <v>2.444212</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>2.881793</v>
+        <v>2.444501</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.00061</v>
+        <v>-0.000633</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000581</v>
+        <v>-0.00061</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051898</v>
+        <v>0.051878</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051921</v>
+        <v>0.051898</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2014</v>
+        <v>5.2043</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2008</v>
+        <v>5.2037</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>2.444212</v>
+        <v>2.501329</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>2.444501</v>
+        <v>2.501625</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000633</v>
+        <v>-0.000653</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.00061</v>
+        <v>-0.000633</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051878</v>
+        <v>0.051861</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051898</v>
+        <v>0.051878</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2043</v>
+        <v>5.1714</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2037</v>
+        <v>5.1708</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>2.501329</v>
+        <v>1.853347</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>2.501625</v>
+        <v>1.853566</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000653</v>
+        <v>-0.00067</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000633</v>
+        <v>-0.000653</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051861</v>
+        <v>0.051847</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051878</v>
+        <v>0.051861</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1714</v>
+        <v>5.1862</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1708</v>
+        <v>5.1856</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>1.853347</v>
+        <v>2.144841</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>1.853566</v>
+        <v>2.145094</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.00067</v>
+        <v>-0.000684</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000653</v>
+        <v>-0.00067</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051847</v>
+        <v>0.051834</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051861</v>
+        <v>0.051847</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1862</v>
+        <v>5.1625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1856</v>
+        <v>5.1619</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>2.144841</v>
+        <v>1.678057</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>2.145094</v>
+        <v>1.678256</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000684</v>
+        <v>-0.000697</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.00067</v>
+        <v>-0.000684</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,29 +499,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01993</v>
+        <v>0.87</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051847</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>0.88</v>
+        <v>97.01608</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>97.01608</v>
+        <v>99.19190999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>99.19190999999999</v>
+        <v>5.1433</v>
       </c>
       <c r="F9" t="n">
-        <v>109.89427</v>
+        <v>5.1512</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1625</v>
+        <v>5.1506</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1619</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="F12" t="n">
-        <v>7355800</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="F13" t="n">
-        <v>2749001</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F16" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F17" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F18" t="n">
-        <v>33.44</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>370395</v>
+        <v>-0.064886</v>
       </c>
       <c r="F19" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.064886</v>
+        <v>-2.103216</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.103216</v>
+        <v>5.757004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>1.455498</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F22" t="n">
-        <v>1.678057</v>
+        <v>1.45567</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F23" t="n">
-        <v>1.678256</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F24" t="n">
-        <v>0.714468</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F25" t="n">
-        <v>1.515494</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F26" t="n">
-        <v>0.242446</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.443025</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F29" t="n">
-        <v>2.772183</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>10.124804</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.098046</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.000697</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001073</v>
+        <v>-0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000697</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001073</v>
+        <v>-0.13</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000684</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -493,35 +493,35 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051834</v>
+        <v>0.051814</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.87</v>
+        <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051823</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -534,16 +534,16 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.16</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -556,38 +556,38 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>97.01608</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>110.22154</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>99.19190999999999</v>
+        <v>97.01608</v>
       </c>
       <c r="F8" t="n">
-        <v>109.89427</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1433</v>
+        <v>99.19190999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1512</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1427</v>
+        <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1506</v>
+        <v>5.149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4346060</v>
+        <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>7355800</v>
+        <v>5.1484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1851006</v>
+        <v>4346060</v>
       </c>
       <c r="F12" t="n">
-        <v>2749001</v>
+        <v>7355800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2495054</v>
+        <v>1851006</v>
       </c>
       <c r="F13" t="n">
-        <v>4606799</v>
+        <v>2749001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.37</v>
+        <v>2495054</v>
       </c>
       <c r="F14" t="n">
-        <v>4.68</v>
+        <v>4606799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="F15" t="n">
-        <v>3.19</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>5.57</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,60 +798,60 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.92</v>
+        <v>2.96</v>
       </c>
       <c r="F17" t="n">
-        <v>33.44</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>370395</v>
+        <v>20.92</v>
       </c>
       <c r="F18" t="n">
-        <v>369742</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.064886</v>
+        <v>370395</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.103216</v>
+        <v>-0.064886</v>
       </c>
       <c r="F20" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>5.757004</v>
+        <v>-2.103216</v>
       </c>
       <c r="F21" t="n">
-        <v>1.455498</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757676</v>
+        <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>1.45567</v>
+        <v>1.412168</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>2.185796</v>
+        <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.714468</v>
+        <v>1.412335</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.329166</v>
+        <v>2.185796</v>
       </c>
       <c r="F24" t="n">
-        <v>1.515494</v>
+        <v>0.714468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,60 +974,60 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.079394</v>
+        <v>2.329166</v>
       </c>
       <c r="F25" t="n">
-        <v>0.242446</v>
+        <v>1.515494</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.407403</v>
+        <v>2.079394</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.242446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>10.069235</v>
+        <v>-0.407403</v>
       </c>
       <c r="F27" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1040,16 +1040,16 @@
         <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>10.074751</v>
+        <v>10.069235</v>
       </c>
       <c r="F28" t="n">
-        <v>2.772183</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1062,38 +1062,38 @@
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.124804</v>
+        <v>10.074751</v>
       </c>
       <c r="F29" t="n">
-        <v>4.098046</v>
+        <v>2.772183</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>10.124804</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.25</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001073</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000697</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.03</v>
+        <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.06</v>
+        <v>-0.000717</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.13</v>
+        <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06</v>
+        <v>-0.000708</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.5</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.22</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051814</v>
+        <v>0.051805</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051823</v>
+        <v>0.051805</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.149</v>
+        <v>5.1642</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1484</v>
+        <v>5.1637</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>1.412168</v>
+        <v>1.71154</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>1.412335</v>
+        <v>1.713712</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000717</v>
+        <v>-0.000726</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000708</v>
+        <v>-0.000726</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051805</v>
+        <v>0.051798</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051805</v>
+        <v>0.051798</v>
       </c>
     </row>
     <row r="5">
@@ -550,16 +550,16 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>0.66</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.16</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="7">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1642</v>
+        <v>5.2005</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1637</v>
+        <v>5.1999</v>
       </c>
     </row>
     <row r="12">
@@ -682,16 +682,16 @@
         <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
         <v>4346060</v>
       </c>
       <c r="F12" t="n">
-        <v>7355800</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
@@ -704,16 +704,16 @@
         <v>44439</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
         <v>1851006</v>
       </c>
       <c r="F13" t="n">
-        <v>2749001</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
@@ -726,16 +726,16 @@
         <v>44439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
         <v>2495054</v>
       </c>
       <c r="F14" t="n">
-        <v>4606799</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
@@ -748,16 +748,16 @@
         <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
         <v>2.37</v>
       </c>
       <c r="F15" t="n">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
@@ -770,16 +770,16 @@
         <v>44439</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
         <v>1.56</v>
       </c>
       <c r="F16" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
@@ -792,16 +792,16 @@
         <v>44439</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
         <v>2.96</v>
       </c>
       <c r="F17" t="n">
-        <v>5.57</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
@@ -814,16 +814,16 @@
         <v>44439</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
         <v>20.92</v>
       </c>
       <c r="F18" t="n">
-        <v>33.44</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
@@ -911,7 +911,7 @@
         <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>1.71154</v>
+        <v>2.426487</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>1.713712</v>
+        <v>2.426773</v>
       </c>
     </row>
     <row r="24">
@@ -946,16 +946,16 @@
         <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
         <v>2.185796</v>
       </c>
       <c r="F24" t="n">
-        <v>0.714468</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
@@ -968,16 +968,16 @@
         <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
         <v>2.329166</v>
       </c>
       <c r="F25" t="n">
-        <v>1.515494</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
@@ -990,16 +990,16 @@
         <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>2.079394</v>
       </c>
       <c r="F26" t="n">
-        <v>0.242446</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
@@ -1056,16 +1056,16 @@
         <v>44773</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
         <v>10.074751</v>
       </c>
       <c r="F29" t="n">
-        <v>2.772183</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
@@ -1131,7 +1131,7 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000726</v>
+        <v>-0.000733</v>
       </c>
     </row>
     <row r="33">
@@ -1153,7 +1153,7 @@
         <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000726</v>
+        <v>-0.000733</v>
       </c>
     </row>
     <row r="34">
@@ -1166,16 +1166,16 @@
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
         <v>-0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
@@ -1188,16 +1188,16 @@
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
         <v>-0.13</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="36">
@@ -1210,16 +1210,16 @@
         <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
         <v>0.05</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.05</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="37">
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
         <v>0.5</v>
       </c>
       <c r="F37" t="n">
-        <v>0.22</v>
+        <v>-1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
         <v>0.01993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051798</v>
+        <v>0.051791</v>
       </c>
     </row>
     <row r="4">
@@ -807,7 +807,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>370395</v>
+        <v>-0.064886</v>
       </c>
       <c r="F19" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.064886</v>
+        <v>-2.103216</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.103216</v>
+        <v>5.757004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>2.426487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F22" t="n">
-        <v>2.426487</v>
+        <v>2.426773</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F23" t="n">
-        <v>2.426773</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.443025</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>10.124804</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.098046</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.00074</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001073</v>
+        <v>-0.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000733</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,54 +1194,10 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>59</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F36" t="n">
         <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>59</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,7 +807,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>370395</v>
+        <v>20.92</v>
       </c>
       <c r="F18" t="n">
-        <v>369742</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.064886</v>
+        <v>370395</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.103216</v>
+        <v>-0.064886</v>
       </c>
       <c r="F20" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>5.757004</v>
+        <v>-2.103216</v>
       </c>
       <c r="F21" t="n">
-        <v>2.426487</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757676</v>
+        <v>5.757004</v>
       </c>
       <c r="F22" t="n">
-        <v>2.426773</v>
+        <v>2.426487</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>2.185796</v>
+        <v>5.757676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>2.426773</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>2.329166</v>
+        <v>2.185796</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>2.079394</v>
+        <v>2.329166</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.407403</v>
+        <v>2.079394</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>10.069235</v>
+        <v>-0.407403</v>
       </c>
       <c r="F27" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>10.074751</v>
+        <v>10.069235</v>
       </c>
       <c r="F28" t="n">
-        <v>2.178243</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>10.124804</v>
+        <v>10.074751</v>
       </c>
       <c r="F29" t="n">
-        <v>4.098046</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>10.124804</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.25</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001073</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.00074</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1131,35 +1131,35 @@
         <v>0.001073</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000733</v>
+        <v>-0.00074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.03</v>
+        <v>0.001073</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3</v>
+        <v>-0.000733</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.13</v>
+        <v>-0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,10 +1194,54 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>59</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.05</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F36" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
         <v>0.01993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051798</v>
+        <v>0.051791</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         <v>5.1433</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2005</v>
+        <v>5.1816</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.1427</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1999</v>
+        <v>5.181</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>370395</v>
+        <v>-0.064886</v>
       </c>
       <c r="F19" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.064886</v>
+        <v>-2.103216</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.103216</v>
+        <v>5.757004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>2.054241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F22" t="n">
-        <v>2.426487</v>
+        <v>2.054484</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F23" t="n">
-        <v>2.426773</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F28" t="n">
-        <v>4.443025</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>10.124804</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.098046</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,16 +1106,16 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>-0.00074</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1137,29 +1137,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001073</v>
+        <v>-0.13</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000733</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>59</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>59</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,16 +459,16 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="F2" t="n">
         <v>14</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01993</v>
+        <v>0.021003</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051791</v>
+        <v>0.051784</v>
       </c>
     </row>
     <row r="4">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01993</v>
+        <v>0.021003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051791</v>
+        <v>0.051784</v>
       </c>
     </row>
     <row r="5">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
         <v>0.07000000000000001</v>
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="F6" t="n">
         <v>-0.22</v>
@@ -569,16 +569,16 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
         <v>-0.01</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.01608</v>
+        <v>96.95313</v>
       </c>
       <c r="F8" t="n">
         <v>110.22154</v>
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>99.19190999999999</v>
+        <v>97.10569</v>
       </c>
       <c r="F9" t="n">
         <v>109.89427</v>
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1433</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
         <v>5.1816</v>
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1427</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
         <v>5.181</v>
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4346060</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
         <v>7372243</v>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1851006</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
         <v>2731513</v>
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2495054</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
         <v>4640730</v>
@@ -741,462 +741,506 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>2.96</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>20.92</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>370395</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>369742</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.064886</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.103216</v>
+        <v>0.541272</v>
       </c>
       <c r="F20" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>5.757004</v>
+        <v>-0.59426</v>
       </c>
       <c r="F21" t="n">
-        <v>2.054241</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>5.757676</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>2.054484</v>
+        <v>2.054241</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="n">
         <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>2.185796</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>2.054484</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>2.329166</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.079394</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.407403</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44773</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>10.069235</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>10.074751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>2.178243</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
         <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>10.124804</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>4.098046</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44469</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.25</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D31" t="n">
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001073</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.00074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001073</v>
+        <v>0.00324</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.00074</v>
+        <v>-0.0007470000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
         <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.13</v>
+        <v>0.00324</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.0007470000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D35" t="n">
-        <v>59</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -484,16 +484,16 @@
         <v>44469</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021003</v>
+        <v>0.021057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051784</v>
+        <v>0.05166</v>
       </c>
     </row>
     <row r="4">
@@ -506,16 +506,16 @@
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021003</v>
+        <v>0.021057</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051784</v>
+        <v>0.05166</v>
       </c>
     </row>
     <row r="5">
@@ -638,16 +638,16 @@
         <v>44469</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1816</v>
+        <v>5.157</v>
       </c>
     </row>
     <row r="11">
@@ -660,16 +660,16 @@
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.181</v>
+        <v>5.1564</v>
       </c>
     </row>
     <row r="12">
@@ -902,16 +902,16 @@
         <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>2.054241</v>
+        <v>-0.474757</v>
       </c>
     </row>
     <row r="23">
@@ -924,16 +924,16 @@
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>2.054484</v>
+        <v>-0.474812</v>
       </c>
     </row>
     <row r="24">
@@ -1122,16 +1122,16 @@
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00324</v>
+        <v>0.003187</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0007470000000000001</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="33">
@@ -1144,16 +1144,16 @@
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00324</v>
+        <v>0.003187</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0007470000000000001</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="34">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021057</v>
+        <v>0.021116</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021057</v>
+        <v>0.021116</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.157</v>
+        <v>5.1273</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1564</v>
+        <v>5.1267</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.474757</v>
+        <v>-1.047939</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.474812</v>
+        <v>-1.04806</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003187</v>
+        <v>0.003127</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003187</v>
+        <v>0.003127</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -490,7 +490,7 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.021116</v>
+        <v>0.021182</v>
       </c>
       <c r="F3" t="n">
         <v>0.05166</v>
@@ -512,7 +512,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021116</v>
+        <v>0.021182</v>
       </c>
       <c r="F4" t="n">
         <v>0.05166</v>
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1273</v>
+        <v>5.0962</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1267</v>
+        <v>5.0956</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.047939</v>
+        <v>-1.64814</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.04806</v>
+        <v>-1.64833</v>
       </c>
     </row>
     <row r="24">
@@ -1128,7 +1128,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003127</v>
+        <v>0.003062</v>
       </c>
       <c r="F32" t="n">
         <v>-0.000124</v>
@@ -1150,7 +1150,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003127</v>
+        <v>0.003062</v>
       </c>
       <c r="F33" t="n">
         <v>-0.000124</v>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -647,7 +647,7 @@
         <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0962</v>
+        <v>5.1253</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0956</v>
+        <v>5.1247</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.64814</v>
+        <v>-1.086537</v>
       </c>
     </row>
     <row r="23">
@@ -933,7 +933,7 @@
         <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.64833</v>
+        <v>-1.086663</v>
       </c>
     </row>
     <row r="24">

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>6.25</v>
+        <v>0.021182</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>0.05166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.021182</v>
+        <v>1.16</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05166</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>96.95313</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>96.95313</v>
+        <v>97.10569</v>
       </c>
       <c r="F8" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="F9" t="n">
-        <v>109.89427</v>
+        <v>5.1253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1253</v>
+        <v>5.1247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1247</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F12" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F13" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F18" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>368886</v>
+        <v>0.541272</v>
       </c>
       <c r="F19" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>0.541272</v>
+        <v>-0.59426</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.59426</v>
+        <v>3.74306</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332557</v>
+        <v>-1.086537</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.086537</v>
+        <v>-1.086663</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.086663</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F26" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="F28" t="n">
-        <v>4.443025</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="F29" t="n">
-        <v>2.178243</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>8.825751</v>
+        <v>0.003062</v>
       </c>
       <c r="F30" t="n">
-        <v>4.098046</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_selic_meta</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>0.003062</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003062</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000124</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003062</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000124</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,53 +1194,9 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D36" t="n">
-        <v>58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D37" t="n">
-        <v>58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>

--- a/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
+++ b/data/final/bcb_sgs/resumo_disponibilidade_bcb_sgs.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -468,16 +468,16 @@
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>0.021182</v>
+        <v>6.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05166</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdi</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -499,95 +499,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>cdi</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>1.16</v>
+        <v>0.021182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>igp_m</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.22</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>igp_m</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>96.95313</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>110.22154</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ibc_br</t>
+          <t>ibc_br_sa</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -600,38 +600,38 @@
         <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>97.10569</v>
+        <v>96.95313</v>
       </c>
       <c r="F8" t="n">
-        <v>109.89427</v>
+        <v>110.22154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cambio_venda_usd</t>
+          <t>ibc_br</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4394</v>
+        <v>97.10569</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1253</v>
+        <v>109.89427</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
+          <t>cambio_venda_usd</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -644,38 +644,38 @@
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1247</v>
+        <v>5.1253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>cambio_compra_usd</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F11" t="n">
-        <v>7372243</v>
+        <v>5.1247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -688,16 +688,16 @@
         <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F12" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -710,16 +710,16 @@
         <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F13" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -732,16 +732,16 @@
         <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F14" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inadimplencia_pj</t>
+          <t>inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -754,16 +754,16 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
+          <t>inadimplencia_pj</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -776,16 +776,16 @@
         <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>inadimplencia_pf</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -798,16 +798,16 @@
         <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -820,38 +820,38 @@
         <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F18" t="n">
-        <v>369742</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br_sa</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>0.541272</v>
+        <v>368886</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>var_pct_ibc_br</t>
+          <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -864,38 +864,38 @@
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.59426</v>
+        <v>0.541272</v>
       </c>
       <c r="F20" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var_pct_cambio_venda_usd</t>
+          <t>var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>3.74306</v>
+        <v>-0.59426</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.086537</v>
+        <v>0.332557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>var_pct_cambio_compra_usd</t>
+          <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -908,38 +908,38 @@
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.086663</v>
+        <v>-1.086537</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_total</t>
+          <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.257708</v>
+        <v>-1.086663</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pj</t>
+          <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -952,16 +952,16 @@
         <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var_pct_saldo_credito_pf</t>
+          <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -974,16 +974,16 @@
         <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var_pct_reservas_internacionais</t>
+          <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -996,104 +996,104 @@
         <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.826955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ipca_acum_12m</t>
+          <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.259972</v>
       </c>
       <c r="F27" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>igp_m_acum_12m</t>
+          <t>ipca_acum_12m</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>8.58755</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>2.178243</v>
+        <v>4.443025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inpc_acum_12m</t>
+          <t>igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>8.825751</v>
+        <v>8.58755</v>
       </c>
       <c r="F29" t="n">
-        <v>4.098046</v>
+        <v>2.178243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dif_selic_over</t>
+          <t>inpc_acum_12m</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.003062</v>
+        <v>8.825751</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000124</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dif_cdi</t>
+          <t>dif_selic_meta</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1106,60 +1106,60 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003062</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_total</t>
+          <t>dif_selic_over</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0.003062</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pj</t>
+          <t>dif_cdi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.003062</v>
       </c>
       <c r="F33" t="n">
-        <v>0.13</v>
+        <v>-0.000124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dif_inadimplencia_pf</t>
+          <t>dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1172,16 +1172,16 @@
         <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dif_juros_credito_total</t>
+          <t>dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1194,9 +1194,53 @@
         <v>58</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58</v>
+      </c>
+      <c r="E37" t="n">
         <v>1.47</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>-1.25</v>
       </c>
     </row>
